--- a/data/trans_dic/P33B_R3-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P33B_R3-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,9%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,04; 17,87</t>
+          <t>12,35; 18,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20,13; 25,15</t>
+          <t>20,5; 25,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,88; 20,72</t>
+          <t>17,09; 20,93</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,87; 16,54</t>
+          <t>13,28; 18,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,74; 24,2</t>
+          <t>19,93; 24,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,86; 19,23</t>
+          <t>17,36; 20,48</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,88; 15,31</t>
+          <t>9,89; 14,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,89; 18,9</t>
+          <t>16,43; 21,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,89; 15,97</t>
+          <t>13,8; 17,46</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>21,35%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,22; 21,61</t>
+          <t>16,06; 21,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,84; 24,98</t>
+          <t>21,57; 25,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,2; 22,34</t>
+          <t>19,76; 22,99</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>18,82%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,43; 16,15</t>
+          <t>14,23; 16,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,55; 21,85</t>
+          <t>20,84; 23,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,09; 18,71</t>
+          <t>18,03; 19,66</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>93021</t>
+          <t>101457</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>151598</t>
+          <t>167319</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>244619</t>
+          <t>268777</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>76406; 113363</t>
+          <t>85154; 124131</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>135921; 169884</t>
+          <t>150207; 187295</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>221114; 271382</t>
+          <t>243129; 297749</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>146071</t>
+          <t>162930</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>211555</t>
+          <t>236927</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>357626</t>
+          <t>399857</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>69966; 197086</t>
+          <t>139201; 193006</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>189135; 231843</t>
+          <t>213426; 262105</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>233567; 413417</t>
+          <t>367860; 433820</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>87515</t>
+          <t>96286</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>132154</t>
+          <t>152499</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>219669</t>
+          <t>248785</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>69644; 107862</t>
+          <t>79397; 117760</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>64283; 176388</t>
+          <t>133463; 172610</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>145572; 261545</t>
+          <t>222967; 282064</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>173723</t>
+          <t>184760</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>239190</t>
+          <t>265356</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>412914</t>
+          <t>450117</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>150347; 200244</t>
+          <t>159009; 209795</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>194949; 272926</t>
+          <t>241260; 288860</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>367525; 451074</t>
+          <t>416591; 484703</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>500330</t>
+          <t>545433</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>734497</t>
+          <t>822101</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1234827</t>
+          <t>1367535</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>395284; 558367</t>
+          <t>502273; 593798</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>605619; 799633</t>
+          <t>778040; 864171</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1074122; 1331942</t>
+          <t>1309728; 1428418</t>
         </is>
       </c>
     </row>
